--- a/data/raw/inventory/Week 29/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 29/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,82 +417,82 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ASIN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>afn_fulfillable_quantity</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>afn_inbound_working_quantity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>afn_inbound_shipped_quantity</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>afn_inbound_receiving_quantity</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>afn_reserved_quantity</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>afn_total_quantity</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>afn_unsellable_quantity</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>afn_researching_quantity</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Seller Account</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>SnapshotDate</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
@@ -1090,7 +1078,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F11" t="n">
         <v>350</v>
@@ -1105,10 +1093,10 @@
         <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -1152,10 +1140,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>587</v>
+        <v>597</v>
       </c>
       <c r="F12" t="n">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1170,10 +1158,10 @@
         <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>603</v>
+        <v>612</v>
       </c>
       <c r="L12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
@@ -1524,10 +1512,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F18" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1539,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L18" t="n">
         <v>8</v>
@@ -1589,7 +1577,7 @@
         <v>215</v>
       </c>
       <c r="F19" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G19" t="n">
         <v>10</v>
@@ -1601,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K19" t="n">
         <v>216</v>
@@ -1961,7 +1949,7 @@
         <v>168</v>
       </c>
       <c r="F25" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1973,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
         <v>168</v>
@@ -2950,10 +2938,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="F41" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2965,10 +2953,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K41" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="L41" t="n">
         <v>2</v>
@@ -3012,7 +3000,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F42" t="n">
         <v>137</v>
@@ -3027,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -3136,7 +3124,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F44" t="n">
         <v>286</v>
@@ -3151,10 +3139,10 @@
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K44" t="n">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="L44" t="n">
         <v>22</v>
@@ -3263,7 +3251,7 @@
         <v>31</v>
       </c>
       <c r="F46" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -3275,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K46" t="n">
         <v>32</v>
@@ -3449,7 +3437,7 @@
         <v>45</v>
       </c>
       <c r="F49" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -3461,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K49" t="n">
         <v>45</v>
@@ -4314,10 +4302,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="F63" t="n">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -4329,10 +4317,10 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K63" t="n">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="L63" t="n">
         <v>4</v>
@@ -4500,10 +4488,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F66" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G66" t="n">
         <v>32</v>
@@ -4518,7 +4506,7 @@
         <v>23</v>
       </c>
       <c r="K66" t="n">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="L66" t="n">
         <v>15</v>
@@ -4748,7 +4736,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -4763,10 +4751,10 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K70" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L70" t="n">
         <v>2</v>
@@ -5058,10 +5046,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="F75" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -5073,10 +5061,10 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K75" t="n">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="L75" t="n">
         <v>17</v>
@@ -5572,10 +5560,10 @@
         <v>1</v>
       </c>
       <c r="K83" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M83" t="n">
         <v>1</v>
@@ -6732,7 +6720,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="F102" t="n">
         <v>113</v>
@@ -6741,7 +6729,7 @@
         <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
@@ -6750,7 +6738,7 @@
         <v>1</v>
       </c>
       <c r="K102" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="L102" t="n">
         <v>1</v>
@@ -6794,7 +6782,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F103" t="n">
         <v>258</v>
@@ -6809,10 +6797,10 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K103" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L103" t="n">
         <v>2</v>
@@ -7166,10 +7154,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F109" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G109" t="n">
         <v>37</v>
@@ -7181,10 +7169,10 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K109" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="L109" t="n">
         <v>6</v>
@@ -7352,7 +7340,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F112" t="n">
         <v>36</v>
@@ -7367,10 +7355,10 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -7414,7 +7402,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F113" t="n">
         <v>146</v>
@@ -7429,10 +7417,10 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K113" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
@@ -7538,7 +7526,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F115" t="n">
         <v>27</v>
@@ -7553,10 +7541,10 @@
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K115" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L115" t="n">
         <v>4</v>
@@ -8468,10 +8456,10 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F130" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -8486,7 +8474,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="L130" t="n">
         <v>2</v>
@@ -8530,7 +8518,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F131" t="n">
         <v>175</v>
@@ -8545,10 +8533,10 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L131" t="n">
         <v>2</v>
@@ -8796,10 +8784,10 @@
         <v>3</v>
       </c>
       <c r="K135" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M135" t="n">
         <v>0</v>
@@ -8967,19 +8955,19 @@
         <v>25</v>
       </c>
       <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
         <v>25</v>
-      </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" t="n">
-        <v>0</v>
       </c>
       <c r="K138" t="n">
         <v>25</v>
@@ -9832,10 +9820,10 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F152" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -9850,7 +9838,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -10018,10 +10006,10 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F155" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G155" t="n">
         <v>12</v>
@@ -10033,10 +10021,10 @@
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K155" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L155" t="n">
         <v>1</v>
@@ -10765,7 +10753,7 @@
         <v>32</v>
       </c>
       <c r="F167" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -10777,7 +10765,7 @@
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K167" t="n">
         <v>32</v>
@@ -10951,7 +10939,7 @@
         <v>48</v>
       </c>
       <c r="F170" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -10963,7 +10951,7 @@
         <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K170" t="n">
         <v>48</v>
@@ -11196,7 +11184,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F174" t="n">
         <v>75</v>
@@ -11211,10 +11199,10 @@
         <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L174" t="n">
         <v>3</v>
@@ -12005,7 +11993,7 @@
         <v>48</v>
       </c>
       <c r="F187" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -12017,7 +12005,7 @@
         <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K187" t="n">
         <v>48</v>

--- a/data/raw/inventory/Week 29/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 29/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -1081,7 +1081,7 @@
         <v>408</v>
       </c>
       <c r="F11" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
         <v>409</v>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>597</v>
+        <v>625</v>
       </c>
       <c r="F12" t="n">
-        <v>523</v>
+        <v>551</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1158,7 +1158,7 @@
         <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>612</v>
+        <v>640</v>
       </c>
       <c r="L12" t="n">
         <v>15</v>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F18" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1527,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="L18" t="n">
         <v>8</v>
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F23" t="n">
         <v>60</v>
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F25" t="n">
         <v>126</v>
@@ -1961,10 +1961,10 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         <v>30</v>
       </c>
       <c r="F40" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G40" t="n">
         <v>5</v>
@@ -2891,7 +2891,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>30</v>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F41" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2953,10 +2953,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K41" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L41" t="n">
         <v>2</v>
@@ -4302,10 +4302,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="F63" t="n">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -4320,7 +4320,7 @@
         <v>8</v>
       </c>
       <c r="K63" t="n">
-        <v>323</v>
+        <v>347</v>
       </c>
       <c r="L63" t="n">
         <v>4</v>
@@ -4550,25 +4550,25 @@
         </is>
       </c>
       <c r="E67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>5</v>
+      </c>
+      <c r="K67" t="n">
         <v>6</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>6</v>
-      </c>
-      <c r="K67" t="n">
-        <v>7</v>
       </c>
       <c r="L67" t="n">
         <v>1</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -4751,10 +4751,10 @@
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L70" t="n">
         <v>2</v>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="F75" t="n">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -5061,10 +5061,10 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K75" t="n">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="L75" t="n">
         <v>17</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="E77" t="n">
+        <v>48</v>
+      </c>
+      <c r="F77" t="n">
         <v>47</v>
-      </c>
-      <c r="F77" t="n">
-        <v>46</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
         <v>1</v>
       </c>
       <c r="K77" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -5542,7 +5542,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F83" t="n">
         <v>222</v>
@@ -5557,10 +5557,10 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L83" t="n">
         <v>1</v>
@@ -7157,7 +7157,7 @@
         <v>222</v>
       </c>
       <c r="F109" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G109" t="n">
         <v>37</v>
@@ -7169,7 +7169,7 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K109" t="n">
         <v>228</v>
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F113" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -7417,10 +7417,10 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K113" t="n">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
@@ -7960,7 +7960,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F122" t="n">
         <v>55</v>
@@ -7975,10 +7975,10 @@
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L122" t="n">
         <v>2</v>
@@ -8409,7 +8409,7 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K129" t="n">
         <v>202</v>
@@ -8418,7 +8418,7 @@
         <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
@@ -10006,10 +10006,10 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F155" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G155" t="n">
         <v>12</v>
@@ -10024,7 +10024,7 @@
         <v>12</v>
       </c>
       <c r="K155" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L155" t="n">
         <v>1</v>

--- a/data/raw/inventory/Week 29/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 29/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P198"/>
+  <dimension ref="A1:P197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="F11" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -1093,10 +1093,10 @@
         <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>625</v>
+        <v>663</v>
       </c>
       <c r="F12" t="n">
-        <v>551</v>
+        <v>590</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1155,13 +1155,13 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>640</v>
+        <v>677</v>
       </c>
       <c r="L12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
@@ -1512,7 +1512,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>209</v>
+        <v>122</v>
       </c>
       <c r="F18" t="n">
         <v>108</v>
@@ -1521,19 +1521,19 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K18" t="n">
-        <v>217</v>
+        <v>129</v>
       </c>
       <c r="L18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
         <v>3</v>
@@ -1825,7 +1825,7 @@
         <v>61</v>
       </c>
       <c r="F23" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>61</v>
@@ -1946,10 +1946,10 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F25" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1961,10 +1961,10 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2445,7 +2445,7 @@
         <v>97</v>
       </c>
       <c r="F33" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K33" t="n">
         <v>97</v>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F36" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="F38" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -2770,7 +2770,7 @@
         <v>22</v>
       </c>
       <c r="K38" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2876,10 +2876,10 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F40" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G40" t="n">
         <v>5</v>
@@ -2894,7 +2894,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="F41" t="n">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2953,10 +2953,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K41" t="n">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="L41" t="n">
         <v>2</v>
@@ -3003,7 +3003,7 @@
         <v>137</v>
       </c>
       <c r="F42" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3015,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>137</v>
@@ -3127,7 +3127,7 @@
         <v>477</v>
       </c>
       <c r="F44" t="n">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -3139,7 +3139,7 @@
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>499</v>
@@ -3434,10 +3434,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F49" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -3452,7 +3452,7 @@
         <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -3561,7 +3561,7 @@
         <v>112</v>
       </c>
       <c r="F51" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K51" t="n">
         <v>113</v>
@@ -4119,7 +4119,7 @@
         <v>198</v>
       </c>
       <c r="F60" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -4131,13 +4131,13 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
+        <v>2</v>
+      </c>
+      <c r="K60" t="n">
+        <v>199</v>
+      </c>
+      <c r="L60" t="n">
         <v>1</v>
-      </c>
-      <c r="K60" t="n">
-        <v>198</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -4302,10 +4302,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="F63" t="n">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -4320,7 +4320,7 @@
         <v>8</v>
       </c>
       <c r="K63" t="n">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="L63" t="n">
         <v>4</v>
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -4382,13 +4382,13 @@
         <v>6</v>
       </c>
       <c r="K64" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F65" t="n">
         <v>28</v>
@@ -4441,10 +4441,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -4488,10 +4488,10 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="F66" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G66" t="n">
         <v>32</v>
@@ -4503,10 +4503,10 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="K66" t="n">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="L66" t="n">
         <v>15</v>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -4565,10 +4565,10 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K67" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L67" t="n">
         <v>1</v>
@@ -4615,7 +4615,7 @@
         <v>18</v>
       </c>
       <c r="F68" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
         <v>18</v>
@@ -4925,7 +4925,7 @@
         <v>21</v>
       </c>
       <c r="F73" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -4937,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
         <v>21</v>
@@ -5046,11 +5046,11 @@
         </is>
       </c>
       <c r="E75" t="n">
+        <v>367</v>
+      </c>
+      <c r="F75" t="n">
         <v>332</v>
       </c>
-      <c r="F75" t="n">
-        <v>309</v>
-      </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
@@ -5061,13 +5061,13 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="K75" t="n">
-        <v>349</v>
+        <v>386</v>
       </c>
       <c r="L75" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -5170,7 +5170,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F77" t="n">
         <v>47</v>
@@ -5185,10 +5185,10 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -5418,10 +5418,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F81" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -5436,7 +5436,7 @@
         <v>3</v>
       </c>
       <c r="K81" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L81" t="n">
         <v>6</v>
@@ -5545,7 +5545,7 @@
         <v>229</v>
       </c>
       <c r="F83" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -5557,7 +5557,7 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83" t="n">
         <v>230</v>
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F93" t="n">
         <v>26</v>
@@ -6177,10 +6177,10 @@
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K93" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -6785,7 +6785,7 @@
         <v>259</v>
       </c>
       <c r="F103" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -6797,13 +6797,13 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K103" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
@@ -6909,7 +6909,7 @@
         <v>18</v>
       </c>
       <c r="F105" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -6921,7 +6921,7 @@
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
         <v>19</v>
@@ -7154,10 +7154,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F109" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G109" t="n">
         <v>37</v>
@@ -7169,10 +7169,10 @@
         <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K109" t="n">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="L109" t="n">
         <v>6</v>
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F113" t="n">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -7417,10 +7417,10 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K113" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F114" t="n">
         <v>27</v>
@@ -7479,10 +7479,10 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K114" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>1</v>
       </c>
       <c r="K115" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
@@ -8273,7 +8273,7 @@
         <v>13</v>
       </c>
       <c r="F127" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -8285,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K127" t="n">
         <v>16</v>
@@ -8335,7 +8335,7 @@
         <v>104</v>
       </c>
       <c r="F128" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -8347,7 +8347,7 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K128" t="n">
         <v>105</v>
@@ -8397,7 +8397,7 @@
         <v>202</v>
       </c>
       <c r="F129" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -8409,7 +8409,7 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K129" t="n">
         <v>202</v>
@@ -8459,7 +8459,7 @@
         <v>43</v>
       </c>
       <c r="F130" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -8471,7 +8471,7 @@
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130" t="n">
         <v>45</v>
@@ -8536,10 +8536,10 @@
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L131" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M131" t="n">
         <v>0</v>
@@ -8769,7 +8769,7 @@
         <v>121</v>
       </c>
       <c r="F135" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -8781,13 +8781,13 @@
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K135" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L135" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M135" t="n">
         <v>0</v>
@@ -8809,12 +8809,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>FBA79265</t>
+          <t>FBA79267</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>B0D2LHNS9B</t>
+          <t>B0D2LD6BYJ</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8824,14 +8824,14 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>CR-01</t>
+          <t>T-02</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -8846,7 +8846,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -8871,12 +8871,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>FBA79267</t>
+          <t>FBA79268</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>B0D2LD6BYJ</t>
+          <t>B0D383WQPB</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8886,14 +8886,14 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>T-02</t>
+          <t>GS-05</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F137" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -8905,10 +8905,10 @@
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K137" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -8933,12 +8933,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FBA79268</t>
+          <t>FBA79271</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>B0D383WQPB</t>
+          <t>B0D83Q7L8W</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8948,14 +8948,14 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>GS-05</t>
+          <t>V-01</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -8967,10 +8967,10 @@
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -8995,12 +8995,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FBA79271</t>
+          <t>FBA79272</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B0D83Q7L8W</t>
+          <t>B0D2LFMY48</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>V-01</t>
+          <t>HS-01</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -9057,12 +9057,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FBA79272</t>
+          <t>FBA79276</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>B0D2LFMY48</t>
+          <t>B0D2LJSQXZ</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9072,14 +9072,14 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>HS-01</t>
+          <t>SM-01</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F140" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -9094,7 +9094,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -9119,12 +9119,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>FBA79276</t>
+          <t>FBA79277</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>B0D2LJSQXZ</t>
+          <t>B0D672NXC8</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9134,14 +9134,14 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>SM-01</t>
+          <t>SC-03</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -9156,7 +9156,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -9181,12 +9181,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>FBA79277</t>
+          <t>FBA79279</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>B0D672NXC8</t>
+          <t>B0D8445KJN</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9196,14 +9196,14 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>SC-03</t>
+          <t>LR-01</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -9215,10 +9215,10 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -9243,12 +9243,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FBA79279</t>
+          <t>FBA79280</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>B0D8445KJN</t>
+          <t>B0D845B2DG</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9258,14 +9258,14 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LR-01</t>
+          <t>LR-02</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F143" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -9277,10 +9277,10 @@
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -9305,12 +9305,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>FBA79280</t>
+          <t>FBA79332</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>B0D845B2DG</t>
+          <t>B0D63FKYZ5</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9320,14 +9320,14 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LR-02</t>
+          <t>HM-01</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -9342,7 +9342,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -9367,12 +9367,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FBA79332</t>
+          <t>FBA79346</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>B0D63FKYZ5</t>
+          <t>B0D25LNDSY</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>HM-01</t>
+          <t>ETC-04-WH</t>
         </is>
       </c>
       <c r="E145" t="n">
@@ -9429,12 +9429,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>FBA79346</t>
+          <t>FBA79349</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>B0D25LNDSY</t>
+          <t>B0D9KDQCCM</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9444,14 +9444,14 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ETC-04-WH</t>
+          <t>SW-01</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -9466,7 +9466,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L146" t="n">
         <v>0</v>
@@ -9491,12 +9491,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>FBA79349</t>
+          <t>FBA79373</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>B0D9KDQCCM</t>
+          <t>B0D2P5TGWK</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9506,14 +9506,14 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>SW-01</t>
+          <t>ET-01-BK</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -9528,7 +9528,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -9553,12 +9553,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FBA79373</t>
+          <t>FBA79374</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>B0D2P5TGWK</t>
+          <t>B0D2P7WLJB</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9568,14 +9568,14 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ET-01-BK</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -9590,7 +9590,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -9615,12 +9615,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FBA79374</t>
+          <t>FBA79404</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>B0D2P7WLJB</t>
+          <t>B0D9KFZYG8</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9630,14 +9630,14 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ET-02-GN</t>
+          <t>FS-01</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F149" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -9649,13 +9649,13 @@
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K149" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M149" t="n">
         <v>0</v>
@@ -9677,12 +9677,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FBA79404</t>
+          <t>FBA79405</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>B0D9KFZYG8</t>
+          <t>B0D9KFP4MG</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9692,14 +9692,14 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>FS-01</t>
+          <t>HSB-03</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F150" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -9714,10 +9714,10 @@
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
@@ -9739,12 +9739,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FBA79405</t>
+          <t>FBA79406</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>B0D9KFP4MG</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9754,11 +9754,11 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>HSB-03</t>
+          <t>HSB-04</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F151" t="n">
         <v>11</v>
@@ -9773,10 +9773,10 @@
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K151" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -9801,12 +9801,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FBA79406</t>
+          <t>FBA79439</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>B0DCK3N2JJ</t>
+          <t>B0DCK7ZH5P</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9816,14 +9816,14 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>HSB-04</t>
+          <t>MR-02</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="F152" t="n">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -9835,16 +9835,16 @@
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K152" t="n">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N152" t="inlineStr">
         <is>
@@ -9863,12 +9863,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FBA79439</t>
+          <t>FBA79440</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>B0DCK7ZH5P</t>
+          <t>B0DCGHKRXX</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9878,14 +9878,14 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>MR-02</t>
+          <t>LE-02</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="F153" t="n">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -9897,16 +9897,16 @@
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N153" t="inlineStr">
         <is>
@@ -9925,12 +9925,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FBA79440</t>
+          <t>FBA79452</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>B0DCGHKRXX</t>
+          <t>B0DCGHVN81</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9940,32 +9940,32 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LE-02</t>
+          <t>VC-01</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="F154" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H154" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K154" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M154" t="n">
         <v>0</v>
@@ -9987,12 +9987,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FBA79452</t>
+          <t>FBA79463</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>B0DCGHVN81</t>
+          <t>B0DCK56Q85</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -10002,32 +10002,32 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VC-01</t>
+          <t>VC-02</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>92</v>
+        <v>13</v>
       </c>
       <c r="F155" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G155" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I155" t="n">
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="L155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
         <v>0</v>
@@ -10049,12 +10049,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FBA79463</t>
+          <t>FBA79464</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>B0DCK56Q85</t>
+          <t>B0DFCDKMWR</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -10064,14 +10064,14 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VC-02</t>
+          <t>CM-01-BL</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -10086,7 +10086,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -10111,12 +10111,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FBA79464</t>
+          <t>FBA79466</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>B0DFCDKMWR</t>
+          <t>B0DFM4JZV9</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>CM-01-BL</t>
+          <t>TI-01</t>
         </is>
       </c>
       <c r="E157" t="n">
@@ -10173,12 +10173,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FBA79466</t>
+          <t>FBA79469</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>B0DFM4JZV9</t>
+          <t>B0DCK4DR1B</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>TI-01</t>
+          <t>LE-04</t>
         </is>
       </c>
       <c r="E158" t="n">
@@ -10235,12 +10235,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FBA79469</t>
+          <t>FBA79472</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>B0DCK4DR1B</t>
+          <t>B0DFCDZWND</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10250,14 +10250,14 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LE-04</t>
+          <t>CM-02-PR</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -10272,7 +10272,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L159" t="n">
         <v>0</v>
@@ -10297,12 +10297,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FBA79472</t>
+          <t>FBA79473</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>B0DFCDZWND</t>
+          <t>B0DJFH6RTL</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10312,14 +10312,14 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>CM-02-PR</t>
+          <t>TI-02</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -10334,7 +10334,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -10359,12 +10359,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FBA79473</t>
+          <t>FBA79480</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>B0DJFH6RTL</t>
+          <t>B0DDC3GVZW</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10374,11 +10374,11 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>TI-02</t>
+          <t>VC-03</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
@@ -10393,10 +10393,10 @@
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K161" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -10421,12 +10421,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FBA79480</t>
+          <t>FBA79481</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>B0DDC3GVZW</t>
+          <t>B0DFMRG2K4</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10436,14 +10436,14 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VC-03</t>
+          <t>TM-02</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -10455,10 +10455,10 @@
         <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
@@ -10483,12 +10483,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FBA79481</t>
+          <t>FBA79484</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>B0DFMRG2K4</t>
+          <t>B0DNJF1BLS</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10498,14 +10498,14 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>TM-02</t>
+          <t>CF-01</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -10520,7 +10520,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -10545,12 +10545,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FBA79484</t>
+          <t>FBA79488</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>B0DNJF1BLS</t>
+          <t>B0DFCG2VGS</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10560,14 +10560,14 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>CF-01</t>
+          <t>KE-01</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -10582,13 +10582,13 @@
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N164" t="inlineStr">
         <is>
@@ -10607,12 +10607,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FBA79488</t>
+          <t>FBA79489</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>B0DFCG2VGS</t>
+          <t>B0DFD123P5</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10622,14 +10622,14 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>KE-01</t>
+          <t>KE-02</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -10644,13 +10644,13 @@
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N165" t="inlineStr">
         <is>
@@ -10669,12 +10669,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>FBA79489</t>
+          <t>FBA79493</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>B0DFD123P5</t>
+          <t>B0DQCWRG3H</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10684,14 +10684,14 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>KE-02</t>
+          <t>V-03</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F166" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -10703,10 +10703,10 @@
         <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K166" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -10731,12 +10731,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>FBA79493</t>
+          <t>FBA79565</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>B0DQCWRG3H</t>
+          <t>B0DKJZDY72</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10746,14 +10746,14 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>V-03</t>
+          <t>VC-04</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -10765,10 +10765,10 @@
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -10793,12 +10793,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>FBA79565</t>
+          <t>FBA79566</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>B0DKJZDY72</t>
+          <t>B0DKJSCLBD</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10808,14 +10808,14 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VC-04</t>
+          <t>VC-05</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F168" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -10830,7 +10830,7 @@
         <v>0</v>
       </c>
       <c r="K168" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -10855,12 +10855,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>FBA79566</t>
+          <t>FBA79567</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>B0DKJSCLBD</t>
+          <t>B0DNJS23HS</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10870,14 +10870,14 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VC-05</t>
+          <t>SC-04</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="F169" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -10889,10 +10889,10 @@
         <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K169" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="L169" t="n">
         <v>0</v>
@@ -10917,12 +10917,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>FBA79567</t>
+          <t>FBA79570</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>B0DNJS23HS</t>
+          <t>B0DKJXRXKM</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10932,14 +10932,14 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>BR-01</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -10951,10 +10951,10 @@
         <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L170" t="n">
         <v>0</v>
@@ -10979,12 +10979,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>FBA79570</t>
+          <t>FBA79573</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>B0DKJXRXKM</t>
+          <t>B0DKK15YNJ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>BR-01</t>
+          <t>EA-02</t>
         </is>
       </c>
       <c r="E171" t="n">
@@ -11041,12 +11041,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>FBA79573</t>
+          <t>FBA79590</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>B0DKK15YNJ</t>
+          <t>B0DM6BB3VT</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -11056,14 +11056,14 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>EA-02</t>
+          <t>CFM-01</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -11078,13 +11078,13 @@
         <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N172" t="inlineStr">
         <is>
@@ -11103,12 +11103,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FBA79590</t>
+          <t>FBA79652</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>B0DM6BB3VT</t>
+          <t>B0F43P6D23</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11118,14 +11118,14 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>CFM-01</t>
+          <t>SC-05</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2</v>
+        <v>93</v>
       </c>
       <c r="F173" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -11140,13 +11140,13 @@
         <v>1</v>
       </c>
       <c r="K173" t="n">
+        <v>96</v>
+      </c>
+      <c r="L173" t="n">
         <v>3</v>
       </c>
-      <c r="L173" t="n">
-        <v>1</v>
-      </c>
       <c r="M173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N173" t="inlineStr">
         <is>
@@ -11165,12 +11165,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>FBA79652</t>
+          <t>FBA79673</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>B0F43P6D23</t>
+          <t>B0FJG5PFGQ</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11180,14 +11180,14 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>SC-05</t>
+          <t>ETC-07-WH</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="F174" t="n">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -11199,13 +11199,13 @@
         <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K174" t="n">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="L174" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
         <v>0</v>
@@ -11227,12 +11227,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>FBA79673</t>
+          <t>FBA79678</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>B0FJG5PFGQ</t>
+          <t>B0DVCDD5VC</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11242,14 +11242,14 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>ETC-07-WH</t>
+          <t>NP-07</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F175" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -11261,10 +11261,10 @@
         <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K175" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -11289,12 +11289,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>FBA79678</t>
+          <t>FBA79679</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>B0DVCDD5VC</t>
+          <t>B0DVC7VJP1</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11304,14 +11304,14 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NP-07</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F176" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -11326,13 +11326,13 @@
         <v>0</v>
       </c>
       <c r="K176" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N176" t="inlineStr">
         <is>
@@ -11351,12 +11351,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>FBA79679</t>
+          <t>FBA79681</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>B0DVC7VJP1</t>
+          <t>B0DVC968P1</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11366,14 +11366,14 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>HU-01</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -11388,13 +11388,13 @@
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N177" t="inlineStr">
         <is>
@@ -11413,12 +11413,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>FBA79681</t>
+          <t>FBA79682</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>B0DVC968P1</t>
+          <t>B0DVC8NYY2</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11428,14 +11428,14 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>HU-01</t>
+          <t>HU-02</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F178" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -11450,7 +11450,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
@@ -11475,12 +11475,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>FBA79682</t>
+          <t>FBA79683</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>B0DVC8NYY2</t>
+          <t>B0DVC9PRSD</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11490,14 +11490,14 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>HU-02</t>
+          <t>AP-01</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="F179" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -11512,7 +11512,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -11537,12 +11537,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>FBA79683</t>
+          <t>FBA79692</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>B0DVC9PRSD</t>
+          <t>B0DVC58QPZ</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11552,14 +11552,14 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>AP-01</t>
+          <t>AP-03</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="F180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -11571,10 +11571,10 @@
         <v>0</v>
       </c>
       <c r="J180" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="K180" t="n">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -11599,12 +11599,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>FBA79692</t>
+          <t>FBA79698</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>B0DVC58QPZ</t>
+          <t>B0DTK4FY1G</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11614,11 +11614,11 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>AP-03</t>
+          <t>SS-01</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="F181" t="n">
         <v>0</v>
@@ -11633,10 +11633,10 @@
         <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -11661,12 +11661,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>FBA79698</t>
+          <t>FBA79707</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>B0DTK4FY1G</t>
+          <t>B0FJ1ZB4G9</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11676,11 +11676,11 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>SS-01</t>
+          <t>ETC-08-BL</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F182" t="n">
         <v>0</v>
@@ -11695,10 +11695,10 @@
         <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K182" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -11723,12 +11723,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>FBA79707</t>
+          <t>FBA79809</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>B0FJ1ZB4G9</t>
+          <t>B0FJ8SFNRH</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11738,11 +11738,11 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ETC-08-BL</t>
+          <t>KE-03</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="F183" t="n">
         <v>0</v>
@@ -11757,10 +11757,10 @@
         <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="K183" t="n">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="L183" t="n">
         <v>0</v>
@@ -11785,12 +11785,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>FBA79809</t>
+          <t>FBA79811</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>B0FJ8SFNRH</t>
+          <t>B0FSF1N457</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11800,11 +11800,11 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>KE-03</t>
+          <t>MC-01</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="F184" t="n">
         <v>0</v>
@@ -11819,10 +11819,10 @@
         <v>0</v>
       </c>
       <c r="J184" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -11847,12 +11847,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>FBA79811</t>
+          <t>FBA79812</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>B0FSF1N457</t>
+          <t>B0FS6TB7CP</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11862,14 +11862,14 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>MC-01</t>
+          <t>PB-01</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="F185" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -11884,7 +11884,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="L185" t="n">
         <v>0</v>
@@ -11909,12 +11909,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>FBA79812</t>
+          <t>FBA79819</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>B0FS6TB7CP</t>
+          <t>B0FT8R24QM</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11924,14 +11924,14 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>PB-01</t>
+          <t>LR-03</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="F186" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -11943,10 +11943,10 @@
         <v>0</v>
       </c>
       <c r="J186" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K186" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -11971,12 +11971,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>FBA79819</t>
+          <t>FBA79971</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>B0FT8R24QM</t>
+          <t>B0GGHZWMVW</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11986,14 +11986,14 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LR-03</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="F187" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -12005,13 +12005,13 @@
         <v>0</v>
       </c>
       <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>26</v>
+      </c>
+      <c r="L187" t="n">
         <v>3</v>
-      </c>
-      <c r="K187" t="n">
-        <v>48</v>
-      </c>
-      <c r="L187" t="n">
-        <v>0</v>
       </c>
       <c r="M187" t="n">
         <v>0</v>
@@ -12033,12 +12033,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>FBA79971</t>
+          <t>FBA79984</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>B0GGHZWMVW</t>
+          <t>B0GM1CZC7Y</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -12048,14 +12048,14 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>MR-03</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -12070,10 +12070,10 @@
         <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L188" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
         <v>0</v>
@@ -12095,12 +12095,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>FBA79984</t>
+          <t>FBA79989</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>B0GM1CZC7Y</t>
+          <t>B0GN86G345</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -12110,11 +12110,11 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>MR-03</t>
+          <t>CAP-05</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F189" t="n">
         <v>0</v>
@@ -12123,7 +12123,7 @@
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I189" t="n">
         <v>0</v>
@@ -12132,7 +12132,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -12157,12 +12157,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>FBA79989</t>
+          <t>FBA79991</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>B0GN86G345</t>
+          <t>B0GN85NZQN</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12172,20 +12172,20 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>CAP-05</t>
+          <t>DH-01</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F190" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
@@ -12194,7 +12194,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="L190" t="n">
         <v>0</v>
@@ -12219,12 +12219,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>FBA79991</t>
+          <t>FBA79992</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>B0GN85NZQN</t>
+          <t>B0GN94YDY2</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12234,14 +12234,14 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>DH-01</t>
+          <t>ST-02</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F191" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -12281,12 +12281,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>FBA79992</t>
+          <t>FBA79993</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>B0GN94YDY2</t>
+          <t>B0GN8WW6BC</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12296,14 +12296,14 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ST-02</t>
+          <t>ST-03</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F192" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -12318,7 +12318,7 @@
         <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -12343,12 +12343,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FBA79993</t>
+          <t>FBK79271</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>B0GN8WW6BC</t>
+          <t>B0DQ8W1RBV</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12358,14 +12358,14 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>ST-03</t>
+          <t>V-01 RG</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F193" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -12380,10 +12380,10 @@
         <v>0</v>
       </c>
       <c r="K193" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M193" t="n">
         <v>0</v>
@@ -12405,12 +12405,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>FBK79271</t>
+          <t>FBK80024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>B0DQ8W1RBV</t>
+          <t>B0GLHC8CB3</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12420,14 +12420,14 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>V-01 RG</t>
+          <t>SS-02</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F194" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -12442,10 +12442,10 @@
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
         <v>0</v>
@@ -12467,12 +12467,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>FBK80024</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>B0GLHC8CB3</t>
+          <t>B0D67727VG</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12482,14 +12482,14 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>SS-02</t>
+          <t>EA-01</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="F195" t="n">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -12504,7 +12504,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="n">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -12529,12 +12529,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>FBP79350</t>
+          <t>FBA79686</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>B0D67727VG</t>
+          <t>B0DV94R4QD</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12544,14 +12544,14 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>EA-01</t>
+          <t>MGS-02</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -12566,7 +12566,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>VIOMI</t>
+          <t>WHITEMULBERRY</t>
         </is>
       </c>
       <c r="O196" t="inlineStr">
@@ -12591,12 +12591,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>FBA79686</t>
+          <t>FBK79406</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>B0DV94R4QD</t>
+          <t>B0DCK3N2JJ</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>MGS-02</t>
+          <t>HSB-04</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -12647,68 +12647,6 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>FBK79406</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>B0DCK3N2JJ</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Nexlev</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>HSB-04</t>
-        </is>
-      </c>
-      <c r="E198" t="n">
-        <v>0</v>
-      </c>
-      <c r="F198" t="n">
-        <v>0</v>
-      </c>
-      <c r="G198" t="n">
-        <v>0</v>
-      </c>
-      <c r="H198" t="n">
-        <v>0</v>
-      </c>
-      <c r="I198" t="n">
-        <v>0</v>
-      </c>
-      <c r="J198" t="n">
-        <v>0</v>
-      </c>
-      <c r="K198" t="n">
-        <v>0</v>
-      </c>
-      <c r="L198" t="n">
-        <v>0</v>
-      </c>
-      <c r="M198" t="n">
-        <v>0</v>
-      </c>
-      <c r="N198" t="inlineStr">
-        <is>
-          <t>WHITEMULBERRY</t>
-        </is>
-      </c>
-      <c r="O198" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="P198" t="n">
         <v>29</v>
       </c>
     </row>
